--- a/sports_forms/018_fitness_assessment_form--sports_forms.xlsx
+++ b/sports_forms/018_fitness_assessment_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'sedentary'}</t>
+          <t>sedentary</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Sedentary'}</t>
+          <t>Sedentary</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'lightly_active'}</t>
+          <t>lightly_active</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Lightly active'}</t>
+          <t>Lightly active</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'very_active'}</t>
+          <t>very_active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Very active'}</t>
+          <t>Very active</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'extremely_active'}</t>
+          <t>extremely_active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Extremely active'}</t>
+          <t>Extremely active</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'several_times_a_week'}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Several times a week'}</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'7-8_hours'}</t>
+          <t>7-8_hours</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': '7-8 hours'}</t>
+          <t>7-8 hours</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'6-7_hours'}</t>
+          <t>6-7_hours</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': '6-7 hours'}</t>
+          <t>6-7 hours</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_6_hours'}</t>
+          <t>less_than_6_hours</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Less than 6 hours'}</t>
+          <t>Less than 6 hours</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'more_than_8_hours'}</t>
+          <t>more_than_8_hours</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'More than 8 hours'}</t>
+          <t>More than 8 hours</t>
         </is>
       </c>
     </row>
